--- a/Employee_Reports_wi52/Mohamed Shafras Jawlangull Q0517.xlsx
+++ b/Employee_Reports_wi52/Mohamed Shafras Jawlangull Q0517.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1584,11 +1584,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Material request Procedure (Other Trainings)</t>
+          <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
@@ -1661,28 +1661,65 @@
       <c r="E26" s="3" t="inlineStr"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
+          <t>25-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>727</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Material request Procedure (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
           <t>17-Nov-2024</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>17-Nov-2026</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2093,7 +2130,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7905</v>
+        <v>7897</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2188,7 +2225,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2217,7 +2254,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2246,7 +2283,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7900</v>
+        <v>7892</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2275,7 +2312,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2304,7 +2341,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2370,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7900</v>
+        <v>7892</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2362,7 +2399,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2391,7 +2428,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2420,7 +2457,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2449,7 +2486,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2478,7 +2515,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2507,7 +2544,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2536,7 +2573,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2565,7 +2602,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2594,7 +2631,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2623,7 +2660,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2652,7 +2689,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2681,7 +2718,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2710,7 +2747,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2739,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2768,7 +2805,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
